--- a/New folder/(RM)Raw_Material_Purchase_Oder_Planning/GTG_daily_stock_analysis/temp_out1.xlsx
+++ b/New folder/(RM)Raw_Material_Purchase_Oder_Planning/GTG_daily_stock_analysis/temp_out1.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,7 +467,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>150 TEXTURISED POLYESTER</t>
+          <t>150/48 TEXTURISED POLYESTER</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>121</v>
+        <v>121.1</v>
       </c>
     </row>
     <row r="19">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="20">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1013.93</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="21">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>257.3</v>
+        <v>6000.3</v>
       </c>
     </row>
     <row r="23">
@@ -638,9 +638,7 @@
           <t>250 HT CONTINOUS POLYESTER FILAMENT</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -783,15 +781,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>75/2 TXP-TPM 800/700</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
+          <t>75/2 TEXTURISED POLYESTER</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>330.11</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>75/3 TXP-TPM 800/560</t>
+          <t>75/2 TXP-TPM 800/700</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -799,28 +799,36 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>840 HI-TENACITY NYLON 6 YARN</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>704.12</v>
-      </c>
+          <t>75/3 TXP-TPM 800/560</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>840 HI-TENACITY NYLON 66 YARN</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
+          <t>840 HI-TENACITY NYLON 6 YARN</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>704.12</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>840 HI-TENACITY NYLON 66 YARN</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>840 HT CONTINOUS POLYESTER FILAMENT</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="B45" t="n">
         <v>329.88</v>
       </c>
     </row>
